--- a/src/attributions/attributions_ig_traj_197.xlsx
+++ b/src/attributions/attributions_ig_traj_197.xlsx
@@ -1571,25 +1571,25 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02836410610202839</v>
+        <v>0.2177692486704049</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01574214567592357</v>
+        <v>0.02644948769820991</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.006180229193396937</v>
+        <v>-0.04918341673742802</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01015016933851289</v>
+        <v>0.161087358751646</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,25 +1607,25 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.008469882750082177</v>
+        <v>-0.02191234147554474</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00179369914678639</v>
+        <v>0.01753880715516439</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002855393491271444</v>
+        <v>0.162145770653168</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,52 +1634,52 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01683235011897859</v>
+        <v>-0.1723364683324761</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01269727458832887</v>
+        <v>-0.02567704657284633</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.007264088217054495</v>
+        <v>-0.0262896075293613</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01407008406978675</v>
+        <v>-0.215927147510876</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01094235308541608</v>
+        <v>0.003881010312888156</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.005767766994053686</v>
+        <v>0.1818380668739036</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,13 +1688,13 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.009082939230619771</v>
+        <v>0.07536898256446602</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.009491242060642814</v>
+        <v>-0.1405947234050816</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
@@ -1703,37 +1703,37 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.06972339537362615</v>
+        <v>0.7389849439094904</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.02231526032155116</v>
+        <v>-0.2005098519532838</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.02507978660761835</v>
+        <v>-0.2840985277934768</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.01651484911088526</v>
+        <v>-0.06053904000944156</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,43 +1742,43 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.03664218886054162</v>
+        <v>-0.09045355578526514</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.02100159927441089</v>
+        <v>-0.07737899091677124</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03436784572963556</v>
+        <v>0.05666725013200993</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.005948964312822741</v>
+        <v>0.07809115517093299</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.003234214220845602</v>
+        <v>0.1371986883397857</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
@@ -1787,49 +1787,49 @@
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.02472722137296463</v>
+        <v>0.5044176612745562</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0233957269638691</v>
+        <v>-0.07594087829168208</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.003997866797143551</v>
+        <v>-0.15702844751695</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.01159335487824647</v>
+        <v>-0.2132140557639568</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01013887059112811</v>
+        <v>-0.02724322327037332</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01282459439571031</v>
+        <v>0.143706586201122</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1841,46 +1841,46 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.001458337360568516</v>
+        <v>0.02376291032850052</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0009957357676953855</v>
+        <v>-0.02376837553041669</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.001005621928753752</v>
+        <v>-0.006856084623648642</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.007523804026455425</v>
+        <v>-0.1921206454679535</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0105197671677327</v>
+        <v>-0.02914776912395233</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01562495253807003</v>
+        <v>0.1507401106450285</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1895,52 +1895,52 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.003796043023020768</v>
+        <v>-0.08341069882569359</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02072516578921397</v>
+        <v>-0.09326474742785795</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.003228654485412073</v>
+        <v>0.09043378618298317</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.003143437933966828</v>
+        <v>-0.1211694942955956</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01614645747467028</v>
+        <v>-0.004013224170819796</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01299992891383101</v>
+        <v>-0.00196434662889026</v>
       </c>
       <c r="DT3" t="n">
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
@@ -1949,61 +1949,61 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.005295621226329484</v>
+        <v>0.05748314183757527</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.02198440620473694</v>
+        <v>-0.1211586212194651</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002205248451441195</v>
+        <v>0.1083680750792039</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.01025618247976593</v>
+        <v>-0.04458878860702458</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.001106625769786768</v>
+        <v>-0.1259284983041131</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.007919262368444428</v>
+        <v>0.02870661442658565</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.0009461677296386822</v>
+        <v>-0.1241584840258344</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,25 +2012,25 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.005965653368875139</v>
+        <v>-0.1889007273517396</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01103548103077366</v>
+        <v>0.145148320608107</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.003929956222268356</v>
+        <v>-0.2148809749763896</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.009262654999288265</v>
+        <v>-0.05966376097798325</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.01519566818465381</v>
+        <v>0.1352866971665963</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.00292889453151148</v>
+        <v>-0.1649377354294304</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
@@ -2066,67 +2066,67 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.02761501192292625</v>
+        <v>0.005984993031604043</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.009488376210276938</v>
+        <v>0.2029586715265021</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.001945638732641563</v>
+        <v>0.02652757566215967</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.001216404400791102</v>
+        <v>0.00814782398210296</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.01792614092990856</v>
+        <v>0.05799104602103679</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.01494798092605343</v>
+        <v>-0.03274955683991126</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.01368109220167008</v>
+        <v>0.08557251813285643</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1146592885477288</v>
+        <v>-0.1080409822543997</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1286480165956908</v>
+        <v>0.1661477470171955</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05957038620395523</v>
+        <v>0.05527975147093999</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -2167,16 +2167,16 @@
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.03732755053254635</v>
+        <v>-0.04711493834053103</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08666898503536163</v>
+        <v>0.153132560109306</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03843633268569339</v>
+        <v>0.05085194653135787</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -2191,22 +2191,22 @@
         <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08933856016410265</v>
+        <v>-0.06104210464588573</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06901793736709091</v>
+        <v>0.04981928096729782</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.02317078955868345</v>
+        <v>0.04751945865772966</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2215,82 +2215,82 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.01600971604289867</v>
+        <v>-0.08380369029328</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01719415943211381</v>
+        <v>0.1899619805508518</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05714870878430204</v>
+        <v>-0.08316530187495527</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.1062152289487498</v>
+        <v>-0.2373468647303832</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.01431020868596955</v>
+        <v>0.1366362476844161</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.01965704786616877</v>
+        <v>-0.2339561990328771</v>
       </c>
       <c r="AP4" t="n">
         <v>-0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.4176396912653325</v>
+        <v>-0.4285952420222786</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1433622575643765</v>
+        <v>0.286974721968157</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.02378142232766758</v>
+        <v>0.1769877436677093</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>-0</v>
@@ -2302,25 +2302,25 @@
         <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.01230559472167037</v>
+        <v>0.06249602705981108</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1605638262103014</v>
+        <v>-0.008940874665444045</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.2586836297311877</v>
+        <v>0.1101229842697416</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
         <v>-0</v>
@@ -2329,22 +2329,22 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04523223396392321</v>
+        <v>0.06594109044171304</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.008307927928035162</v>
+        <v>-0.04421591017270295</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.05963312621709889</v>
+        <v>0.0187601938573118</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,49 +2356,49 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.2936974695462725</v>
+        <v>-0.3360351731222878</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1237835184332772</v>
+        <v>0.2443503591926172</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01485431347575817</v>
+        <v>0.1081076783007176</v>
       </c>
       <c r="BZ4" t="n">
         <v>-0</v>
       </c>
       <c r="CA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.08280363710274942</v>
+        <v>0.2165596078065386</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.0448552865343537</v>
+        <v>-0.1868633845572712</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001707469105467391</v>
+        <v>0.003120148239200406</v>
       </c>
       <c r="CI4" t="n">
         <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>-0</v>
@@ -2410,19 +2410,19 @@
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007822300898133584</v>
+        <v>-0.03132801918662966</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.009018677218937916</v>
+        <v>0.03295734622498169</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.001457354163895521</v>
+        <v>0.01221141432312177</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2437,22 +2437,22 @@
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.08545771693230904</v>
+        <v>0.2149202664708402</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.05235013124443627</v>
+        <v>-0.1887257102007113</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01984805797386081</v>
+        <v>-0.01434435834230418</v>
       </c>
       <c r="DA4" t="n">
         <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.09396267379599985</v>
+        <v>0.1208132287351903</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.02316349836055663</v>
+        <v>-0.04364506482674052</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.01728867988767442</v>
+        <v>0.06748723391705685</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2488,52 +2488,52 @@
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.1047822476002669</v>
+        <v>0.08917494140262963</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.07532792876821154</v>
+        <v>-0.1048325388885044</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.08151967960977297</v>
+        <v>0.03983267755731373</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="n">
         <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.008473978558080575</v>
+        <v>-0.1061721777236915</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.04045410264282841</v>
+        <v>0.0900099630882009</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02768931018624496</v>
+        <v>-0.09946464795032445</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>-0</v>
@@ -2545,49 +2545,49 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.03254165089274551</v>
+        <v>0.1801720675860319</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0.05108253003444989</v>
+        <v>-0.1310751013308131</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.05500863914573714</v>
+        <v>-0.03973280294077936</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.08373924508847871</v>
+        <v>0.1123182637418547</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.001903682240583605</v>
+        <v>-0.1148642040175984</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.04469231920719909</v>
+        <v>-0.05485010895496398</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
         <v>-0</v>
@@ -2599,22 +2599,22 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.09592569183673927</v>
+        <v>0.2479361569202033</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.07259046090563852</v>
+        <v>-0.2171638241120881</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.635043486856158e-05</v>
+        <v>-0.002425467536355021</v>
       </c>
       <c r="FC4" t="n">
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
@@ -2626,16 +2626,16 @@
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.06639795735578437</v>
+        <v>0.1263379505714167</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.02701856066420762</v>
+        <v>-0.09347887525109914</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01578464252214066</v>
+        <v>-0.002724278050568033</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP4" t="n">
         <v>0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.00375328783761426</v>
+        <v>-0.01183832642339416</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.06895370679087992</v>
+        <v>-0.08457363087634867</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007596555385389124</v>
+        <v>0.01496425709793156</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0336262150440051</v>
+        <v>0.1780573213000152</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.04608028826151383</v>
+        <v>-0.1075961039483313</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3677489009599849</v>
+        <v>0.2175208874077613</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3504532059317336</v>
+        <v>-0.1946555218751643</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0233221593369487</v>
+        <v>-0.0369874237563143</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2736,16 +2736,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2696412374423749</v>
+        <v>0.1789618020839369</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04898882453576299</v>
+        <v>-0.04773606677988591</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03314124578576182</v>
+        <v>-0.05142237715599223</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2763,106 +2763,106 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1311112988754609</v>
+        <v>0.09880482645816675</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.07238044931127909</v>
+        <v>-0.03451527212423976</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1014218036674237</v>
+        <v>-0.1135647343066353</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1548178006205276</v>
+        <v>0.1436716956748875</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02331720815169122</v>
+        <v>-0.1390357100585424</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.02756228436082525</v>
+        <v>-0.02237173444983434</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.07454289057333537</v>
+        <v>0.209496217998229</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.1128486201687022</v>
+        <v>-0.06776289242414202</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.09640296768532655</v>
+        <v>0.09649197278652781</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.635017084785767</v>
+        <v>0.4659863471398105</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.2742225077253</v>
+        <v>-0.2323900611943666</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1037567152749229</v>
+        <v>-0.2809651240682967</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1335985699403563</v>
+        <v>-0.03203792073651861</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.08374850670913829</v>
+        <v>-0.009125882265828313</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1894979115391386</v>
+        <v>-0.1137213535418692</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,16 +2898,16 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02915673961972467</v>
+        <v>0.004241904139879202</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.153142753573395</v>
+        <v>0.02801855671521544</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1430156260768988</v>
+        <v>0.1106315978194538</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.3480176738976931</v>
+        <v>0.2512856112667478</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.1306448727995964</v>
+        <v>-0.1379648211358441</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1354582433111062</v>
+        <v>-0.1111616476824485</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,97 +2952,97 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1434552452331021</v>
+        <v>-0.2003181031837772</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.1036114872746807</v>
+        <v>0.1730713082470746</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.04104074485537931</v>
+        <v>0.03631412583216664</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.00152429532423283</v>
+        <v>0.007453094793583019</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1153141574837289</v>
+        <v>0.3154430598493443</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.02562402252001991</v>
+        <v>-0.02413702801693144</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1537312914136752</v>
+        <v>-0.1835999780371436</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.1269866535954347</v>
+        <v>0.1876049899218146</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0306954127717663</v>
+        <v>0.03779083844641731</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.02738335695252787</v>
+        <v>-0.05305495421844078</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.2386084727951956</v>
+        <v>0.06952777421672617</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.01197792632008032</v>
+        <v>-0.03076444991235778</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
@@ -3054,76 +3054,76 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07830604792867576</v>
+        <v>-0.09840793630250215</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.05145943097704279</v>
+        <v>0.1605725531766948</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.1493577212175214</v>
+        <v>-0.1202185256810944</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1475780643482353</v>
+        <v>-0.1730752499204482</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.08077423801196738</v>
+        <v>-0.1284454605500683</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01382038226471459</v>
+        <v>-0.05857667900525419</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1291026205230037</v>
+        <v>-0.1031833832313281</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.1461439517354103</v>
+        <v>0.1316268869256955</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1053789098098101</v>
+        <v>0.06934976006715972</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
@@ -3132,31 +3132,31 @@
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1676938073948844</v>
+        <v>-0.1279724133637523</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.08505249177521398</v>
+        <v>0.05172583621575594</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.03011751368386842</v>
+        <v>0.08725661261787704</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,46 +3165,46 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.153707043883925</v>
+        <v>-0.2149210693988946</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.1286225771015986</v>
+        <v>0.1990529032385803</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04044882016290289</v>
+        <v>0.02027530336938196</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0802392109149233</v>
+        <v>0.004887196990301099</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.08444292322828899</v>
+        <v>0.06543773851653455</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02929109085378594</v>
+        <v>-0.0534514431426026</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,49 +3213,49 @@
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.04365620616974618</v>
+        <v>0.03086564072701042</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.0407727735901005</v>
+        <v>-0.04944501828570527</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.07045465877623983</v>
+        <v>0.0498109017118428</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.04808979274969779</v>
+        <v>-0.1080042557583665</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01925731298964463</v>
+        <v>0.1340174130344901</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,34 +3275,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.06636576144446024</v>
+        <v>0.07877300079443843</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.07171999088971953</v>
+        <v>-0.1398163715527273</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0360844149756378</v>
+        <v>-0.005985196736730993</v>
       </c>
       <c r="F6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06701313527270722</v>
+        <v>0.03296616654753013</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -3311,25 +3311,25 @@
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01541368708749257</v>
+        <v>-0.1482056174947682</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000443937041095654</v>
+        <v>-0.0176730611024789</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009581446555442116</v>
+        <v>-0.0304840356362495</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -3338,25 +3338,25 @@
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.04615955371283598</v>
+        <v>-0.03010244518369061</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07735018603861173</v>
+        <v>-0.03733067352569401</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.03058208382013231</v>
+        <v>-0.008542674384468289</v>
       </c>
       <c r="AC6" t="n">
         <v>-0</v>
@@ -3365,64 +3365,64 @@
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.01761458518284081</v>
+        <v>0.04794823394926574</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11053569337468</v>
+        <v>0.1261811614297365</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.01118950348305187</v>
+        <v>0.008974474579815482</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.02347875249396835</v>
+        <v>-0.142306601699896</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.08634463882491178</v>
+        <v>0.05937029192787729</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.08008061739555551</v>
+        <v>-0.04193928289219972</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.09573393597779746</v>
+        <v>-0.3322657911256522</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1499924886411066</v>
+        <v>-0.09196753210925607</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3437,46 +3437,46 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.1079630367344464</v>
+        <v>0.2105302321973505</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.00138220381308104</v>
+        <v>0.2072874583781077</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.03460909045870571</v>
+        <v>0.1714465817624088</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0405774224949037</v>
+        <v>0.02850180139576035</v>
       </c>
       <c r="BM6" t="n">
         <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02617051322351845</v>
+        <v>-0.002578555438840701</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1043261428464523</v>
+        <v>-0.1011301435927157</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
@@ -3485,13 +3485,13 @@
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.03343823056623788</v>
+        <v>-0.1024690428374007</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.005435928862125591</v>
+        <v>-0.2932842297794289</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.08994008535656033</v>
+        <v>-0.06331085424432265</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3515,76 +3515,76 @@
         <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.01966870560799617</v>
+        <v>-0.04743076986332124</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.007278574221009271</v>
+        <v>0.1177086323603753</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.01048852142755677</v>
+        <v>0.006214202987633506</v>
       </c>
       <c r="CI6" t="n">
         <v>0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.001330419174987816</v>
+        <v>-0.0004833784199084475</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.00852182754879547</v>
+        <v>0.02069015340336663</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003181239876039678</v>
+        <v>0.004946309672073703</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0115273182077853</v>
+        <v>-0.04143171712585788</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX6" t="n">
         <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01185306432020335</v>
+        <v>0.1130893669096303</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.004565268745464625</v>
+        <v>0.01953008579385643</v>
       </c>
       <c r="DA6" t="n">
         <v>-0</v>
@@ -3596,22 +3596,22 @@
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0127952100652842</v>
+        <v>-0.02642670495532737</v>
       </c>
       <c r="DF6" t="n">
         <v>-0</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.09782529723730481</v>
+        <v>0.1126093275402189</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.07540072806650633</v>
+        <v>-0.02116268756054581</v>
       </c>
       <c r="DJ6" t="n">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.03577417243655969</v>
+        <v>-0.07450536636235776</v>
       </c>
       <c r="DO6" t="n">
         <v>-0</v>
@@ -3635,37 +3635,37 @@
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.01156242568817595</v>
+        <v>0.03502170138246306</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.05889143223081697</v>
+        <v>0.06382114537161224</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.01593245268996971</v>
+        <v>0.07058548583778952</v>
       </c>
       <c r="DX6" t="n">
         <v>-0</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.04766638790165078</v>
+        <v>0.09350739487828373</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01135206206441999</v>
+        <v>0.01226416469231252</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
@@ -3674,55 +3674,55 @@
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001537198366621068</v>
+        <v>-0.1000691951321892</v>
       </c>
       <c r="EG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.02578314479091752</v>
+        <v>0.06618229135940749</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02004514778582348</v>
+        <v>0.0598918299555331</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.02582666400782175</v>
+        <v>0.02966383844310082</v>
       </c>
       <c r="EP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02076117041351176</v>
+        <v>0.09956411904402966</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02790123084445291</v>
+        <v>-0.01499894035805375</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3734,19 +3734,19 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.01032530643189424</v>
+        <v>-0.03694568614490355</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ6" t="n">
         <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.004426456629404261</v>
+        <v>0.1552672459565247</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.00234824514025303</v>
+        <v>0.0151303259890451</v>
       </c>
       <c r="FC6" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0.02307642931700985</v>
+        <v>0.03934085394653749</v>
       </c>
       <c r="FH6" t="n">
         <v>0</v>
@@ -3770,25 +3770,25 @@
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.05271136167130373</v>
+        <v>0.1064474969978791</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.1001704621571519</v>
+        <v>0.1068671582022751</v>
       </c>
       <c r="FL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM6" t="n">
         <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
         <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.004449002928708972</v>
+        <v>0.01140599106763436</v>
       </c>
       <c r="FQ6" t="n">
         <v>0</v>
@@ -3797,10 +3797,10 @@
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.01472586792407627</v>
+        <v>0.2416194188182341</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.02785779916389719</v>
+        <v>0.05997314686224339</v>
       </c>
       <c r="FU6" t="n">
         <v>0</v>
@@ -3812,25 +3812,25 @@
         <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.008183923773370086</v>
+        <v>-0.01029622991351125</v>
       </c>
       <c r="FZ6" t="n">
         <v>0</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.00925030293286511</v>
+        <v>0.2037819516599482</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.251223964341382</v>
+        <v>0.278501340705645</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08970323589631432</v>
+        <v>-0.1158465800187922</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.00424328475297552</v>
+        <v>-0.05303776977066774</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1444685921310474</v>
+        <v>0.2396907270289436</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09608655854124501</v>
+        <v>-0.1537189545205484</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.002205926570495537</v>
+        <v>-0.1053831542437964</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5039,106 +5039,106 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08993691051081219</v>
+        <v>0.07966560891719528</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01442809461491322</v>
+        <v>-0.06072144029982336</v>
       </c>
       <c r="W9" t="n">
-        <v>0.106243715435382</v>
+        <v>-0.07528924357678231</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05850259108613508</v>
+        <v>-0.05926997206934987</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01889339289559727</v>
+        <v>-0.1515065359846119</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.007300983402482081</v>
+        <v>-0.04223820515094325</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0006506486764033065</v>
+        <v>0.1004257538468834</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0574657742168908</v>
+        <v>-0.09000141603760127</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04010395794074042</v>
+        <v>0.07196034604463251</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3328979109134213</v>
+        <v>0.3476466740329139</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.02368829802285582</v>
+        <v>-0.0772018843879647</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1143314167431157</v>
+        <v>-0.2289875157379564</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,25 +5147,25 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.06630013773702177</v>
+        <v>-0.02001386812432811</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1558368509520762</v>
+        <v>-0.02571026944810781</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07340382590965333</v>
+        <v>0.01433682956426678</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08441490581224513</v>
+        <v>0.0007219709764163717</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.05637174143199129</v>
+        <v>0.03572177947362683</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1580865731602937</v>
+        <v>0.05936010603615882</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
@@ -5201,49 +5201,49 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1391783476064896</v>
+        <v>0.2150916022000775</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.01509397885679148</v>
+        <v>-0.1457869749438602</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.08679541255806977</v>
+        <v>-0.07668640877554836</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08407251062967037</v>
+        <v>-0.1446127961902874</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.004750077459781643</v>
+        <v>0.1041921471004205</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01436459921214273</v>
+        <v>0.02660942045042538</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,43 +5255,43 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.007190439404967006</v>
+        <v>-0.02094330917837056</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.034039620116542</v>
+        <v>0.06643917633544733</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.01637678140935584</v>
+        <v>0.00755184548536959</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05808140476318741</v>
+        <v>-0.151607907939995</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02477476396464583</v>
+        <v>0.1185065633863314</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01993948192365586</v>
+        <v>0.03344587110443718</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01883536350077122</v>
+        <v>-0.08421425068339418</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.04132130464349254</v>
+        <v>0.02070946837815783</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05019738166646768</v>
+        <v>-0.1229811220074941</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5330,31 +5330,31 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06601446521663981</v>
+        <v>-0.07485540461063028</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.003487652777654318</v>
+        <v>-0.01658790167369156</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.04105592987470532</v>
+        <v>-0.01524595349305255</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,43 +5363,43 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.05802226736394641</v>
+        <v>-0.04821198062272811</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02351407456221182</v>
+        <v>0.09445306974576717</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01639916950122474</v>
+        <v>0.02278514465794292</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0733020581187859</v>
+        <v>-0.1068028740791116</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.006372882849275957</v>
+        <v>0.07572108536326062</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0519776505079552</v>
+        <v>0.04711560825100662</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.01722815211091778</v>
+        <v>-0.05675395574112688</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.008082584681692801</v>
+        <v>0.0795607816272709</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.04346929205833604</v>
+        <v>-0.00315749527043369</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,28 +5441,28 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0588205293651267</v>
+        <v>-0.1568799473695545</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.007226204706808852</v>
+        <v>0.1440654260840277</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.004788307690456192</v>
+        <v>0.014721592451051</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
@@ -5471,49 +5471,49 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.04638188569061102</v>
+        <v>0.1239581571970062</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0.005804060237115286</v>
+        <v>0.07905749414231615</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01363381096292388</v>
+        <v>0.03445408447839089</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.04296481947781015</v>
+        <v>0.0549607528504138</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01139795455618683</v>
+        <v>0.1845970220884825</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.04003122783022847</v>
+        <v>-0.02577574012692167</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,25 +5522,25 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.04902076533127929</v>
+        <v>-0.07060198381504744</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.0923696988704568</v>
+        <v>0.09450142025093586</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.08310641417951349</v>
+        <v>0.2131066876137017</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,10 +5563,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03216313838832734</v>
+        <v>-0.01491856569305177</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0362497265785134</v>
+        <v>-0.1306991299051517</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -5575,13 +5575,13 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.057818544336913</v>
+        <v>0.2380480409253094</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,97 +5590,97 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02456850250181632</v>
+        <v>-0.07560714897030651</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.02802809757537411</v>
+        <v>-0.1173414089995106</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01035594314559746</v>
+        <v>0.0843540237845872</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01020886067358554</v>
+        <v>-0.08687601577898128</v>
       </c>
       <c r="X10" t="n">
-        <v>0.009961460141354118</v>
+        <v>-0.02604609854941493</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002547805610462322</v>
+        <v>-0.01732811603224808</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.008162141068143322</v>
+        <v>-0.1801857866001301</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.002509989036834116</v>
+        <v>0.02345371336243273</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005248271069389822</v>
+        <v>0.0533111450897723</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01887139046448695</v>
+        <v>-0.03282336681773824</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.01146204268476802</v>
+        <v>-0.03080042071320669</v>
       </c>
       <c r="AQ10" t="n">
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.09212954995069821</v>
+        <v>0.3379958677407696</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,10 +5698,10 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.01500442215337533</v>
+        <v>-0.2292346782713761</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.01907601898840029</v>
+        <v>-0.1259031408400842</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
@@ -5710,13 +5710,13 @@
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02711884100722636</v>
+        <v>-0.01316763680920174</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.0551290733328552</v>
+        <v>-0.001336349948822769</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.04603215083395484</v>
+        <v>-0.08037680528252374</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03147959104426783</v>
+        <v>0.04223458974318645</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,25 +5752,25 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02202143434277098</v>
+        <v>0.07814930356469377</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02086427713889212</v>
+        <v>0.04590886101752193</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04362284195527005</v>
+        <v>0.2037930945098303</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.01253874059975621</v>
+        <v>-0.05296752134303925</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.003227780995567658</v>
+        <v>-0.1407924403718005</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,40 +5791,40 @@
         <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02178577591264249</v>
+        <v>-0.09336147278177868</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002226592609014568</v>
+        <v>0.01918340127296927</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01703489010885884</v>
+        <v>0.0907734853864402</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0003877859856397424</v>
+        <v>-0.03043463546049956</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,145 +5833,145 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.00183834434736538</v>
+        <v>0.0373403478228229</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.004197966611542161</v>
+        <v>0.01836255398537946</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.01513300974820548</v>
+        <v>-0.09558193454091984</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.004532660886922806</v>
+        <v>0.01873733113579069</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.01814571513910464</v>
+        <v>0.1058836991406494</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01233641598011971</v>
+        <v>-0.03475753164738786</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0238148284716293</v>
+        <v>-0.06793943716943583</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.00698107745136299</v>
+        <v>0.05724096786685699</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.004953757249663614</v>
+        <v>-0.02936669562595939</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01320395928101851</v>
+        <v>-0.05450300300687187</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.002638071213612279</v>
+        <v>-0.009886388451631022</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02915698563891814</v>
+        <v>-0.01503569628715744</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01443737457625089</v>
+        <v>0.01452542546512056</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.015636447570216</v>
+        <v>0.05973711693154603</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.0213677806709337</v>
+        <v>-0.04170679222469397</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0106613089610551</v>
+        <v>-0.005721943754977386</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01564814040482138</v>
+        <v>0.03192046098428802</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5983,22 +5983,22 @@
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01029095161933739</v>
+        <v>-0.02140023158187453</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.008836696297493535</v>
+        <v>-0.022498288858734</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.000176528301915933</v>
+        <v>0.094278591933129</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.01550370469195888</v>
+        <v>-0.1075108559636271</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.008541318893444727</v>
+        <v>-0.0008908267785806535</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02178091815782025</v>
+        <v>0.08400913234733369</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
@@ -6040,25 +6040,25 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.0166106987576309</v>
+        <v>0.1409290875667467</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01319679406354791</v>
+        <v>-0.05766876847116088</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.009343837170434252</v>
+        <v>0.092019209415017</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.002016555641107683</v>
+        <v>0.02966466736070963</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
@@ -6076,46 +6076,46 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.01904373844131721</v>
+        <v>-0.06704106144158659</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.003739378310252225</v>
+        <v>-0.0364158183220413</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001194802546424922</v>
+        <v>-0.02756783731404992</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.01426541731117219</v>
+        <v>0.1013062375046133</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3172480201789628</v>
+        <v>0.2962642316067405</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0815293265772702</v>
+        <v>-0.1016133250933527</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06105051945145556</v>
+        <v>-0.03807551292404959</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,22 +6150,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1985349018045286</v>
+        <v>0.3038672099483142</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.07823501855562068</v>
+        <v>-0.1199706029390971</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04482318063540671</v>
+        <v>-0.09217565362012202</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,70 +6177,70 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09605897288104975</v>
+        <v>0.06796692714965753</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.007885175866284379</v>
+        <v>-0.04441040531952951</v>
       </c>
       <c r="W11" t="n">
-        <v>0.09685620105557902</v>
+        <v>-0.09241289382804595</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04699852607200408</v>
+        <v>-0.04039677800252647</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01366636290133523</v>
+        <v>-0.1414195716356985</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.01471018748035188</v>
+        <v>-0.02923958610773691</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.009697232549097342</v>
+        <v>0.08748551692800763</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.04921714665953771</v>
+        <v>-0.08597995761231582</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.03866137790632532</v>
+        <v>0.08032677832935235</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6255,28 +6255,28 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3824816061147518</v>
+        <v>0.2948376845810495</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.04668330416226725</v>
+        <v>-0.06264034249460074</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.08537629421309968</v>
+        <v>-0.2313606969571307</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,25 +6285,25 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04682511908950722</v>
+        <v>0.003282383195566013</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.1495596828675559</v>
+        <v>-0.04870631829619164</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1164306732215636</v>
+        <v>0.008089695594610289</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,76 +6312,76 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.09503646368504559</v>
+        <v>-0.01386652394585569</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.05648332917586762</v>
+        <v>0.03901417531452726</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.152885088406101</v>
+        <v>0.07878745486894699</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1774636412789606</v>
+        <v>0.1715509634083828</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.03321235428200703</v>
+        <v>-0.09388011697056356</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06365268632088375</v>
+        <v>-0.07328198352350995</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.09301711081305199</v>
+        <v>-0.1299371730885736</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.01567389062266165</v>
+        <v>0.09517644172873434</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.002893150770066018</v>
+        <v>0.01771486529900404</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,43 +6393,43 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01051168818729659</v>
+        <v>-0.02503559484947347</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.033330892298005</v>
+        <v>0.06337426872134945</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.03358933046821833</v>
+        <v>0.0187753230548628</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.06167330153550758</v>
+        <v>-0.1323600275619395</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01871110545592778</v>
+        <v>0.1073101230988154</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01190903674853317</v>
+        <v>0.02660148294324376</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01992179605499613</v>
+        <v>-0.06830376091659331</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.04432594714417632</v>
+        <v>0.002088202934910859</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02389734227792708</v>
+        <v>-0.04774097353166562</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6468,31 +6468,31 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.08582627107983541</v>
+        <v>-0.06046990634720081</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0006681540856592905</v>
+        <v>-0.05783056069038959</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.04858378615518138</v>
+        <v>-0.0638716837598096</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,106 +6501,106 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.05327020495283161</v>
+        <v>-0.03019333821581166</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.03115394003832462</v>
+        <v>0.04958250957400383</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.004240902354778486</v>
+        <v>0.01353942974228713</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.07727391316326927</v>
+        <v>-0.094601862472962</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0.004736001922164478</v>
+        <v>0.06526751512442093</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.06793583969391125</v>
+        <v>0.04912395966215129</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.007692936318635136</v>
+        <v>-0.04256833424803707</v>
       </c>
       <c r="EQ11" t="n">
         <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.006191833230437442</v>
+        <v>0.02811515118134604</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03849414834627549</v>
+        <v>0.01380439516898718</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.06115157649450388</v>
+        <v>-0.1364133973131502</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0.0111046149003909</v>
+        <v>0.1301957660618188</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01440168964314525</v>
+        <v>0.002207661921429914</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
@@ -6609,16 +6609,16 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.04429328793458519</v>
+        <v>0.1300268411809754</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>-0.001606220274879326</v>
+        <v>0.1028515732927653</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01075285579607081</v>
+        <v>0.01355841422883728</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6630,69 +6630,69 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.04089630925840685</v>
+        <v>0.03963598935444017</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.02482997317580786</v>
+        <v>0.170026127222647</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.06116314464574977</v>
+        <v>-0.04295959876934477</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.04559657367172094</v>
+        <v>-0.06645852590910777</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.08334760003552595</v>
+        <v>0.04292014785322157</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
         <v>-0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
         <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.206677132272801</v>
+        <v>0.3388495369133573</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03705728150365717</v>
+        <v>0.02821182838974835</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1285381874682162</v>
+        <v>-0.281911115299518</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6716,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1576015028715495</v>
+        <v>0.385659898815425</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,67 +6728,67 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.004979077126752169</v>
+        <v>-0.1126225007277764</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.08968713677147606</v>
+        <v>-0.2623579248341775</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02839964115598057</v>
+        <v>0.132165375204702</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.04474804412423346</v>
+        <v>-0.08683737646628879</v>
       </c>
       <c r="X12" t="n">
-        <v>0.002653951691151286</v>
+        <v>-0.09020002436716439</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.0009176239359008774</v>
+        <v>-0.05661214684699582</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.004334759527918738</v>
+        <v>-0.2054082792293271</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.01784582250028875</v>
+        <v>0.08743487515480518</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03911334028623794</v>
+        <v>0.1371815279794505</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.006589009317252262</v>
+        <v>-0.0220991024643942</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.05462252241717564</v>
+        <v>-0.09927349820418667</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6827,34 +6827,34 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1812355470258812</v>
+        <v>0.6573666488786132</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.04842978974172556</v>
+        <v>-0.2952754630506809</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.1001269921666773</v>
+        <v>-0.2627063310256972</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06702990407762506</v>
+        <v>-0.1313704234337031</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,10 +6863,10 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03732674957549862</v>
+        <v>0.05052334703280346</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.06632529572871407</v>
+        <v>-0.04777531110089105</v>
       </c>
       <c r="BI12" t="n">
         <v>0</v>
@@ -6875,40 +6875,40 @@
         <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.06216351303146184</v>
+        <v>0.1229295860138742</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02396888842301675</v>
+        <v>0.0450683478333687</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01415941579822689</v>
+        <v>0.09085913242436781</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.09940204973801116</v>
+        <v>0.3684554258392129</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.03436342659059179</v>
+        <v>-0.07439352811334179</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.04166698803712526</v>
+        <v>-0.2417767713923085</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6929,79 +6929,79 @@
         <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.0453251825750608</v>
+        <v>-0.1705931747785255</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.005711816878290265</v>
+        <v>0.03968634114752027</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.04754910109626893</v>
+        <v>0.1191042649909655</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002741818149153441</v>
+        <v>-0.1101426803315499</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0002022323359089147</v>
+        <v>0.09325366783204382</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01299234596900842</v>
+        <v>-0.00752805671918708</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04029411386324624</v>
+        <v>-0.1604655767058682</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.003812321253302286</v>
+        <v>0.03062271684376742</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.05235072717673016</v>
+        <v>0.1480636954218339</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7010,25 +7010,25 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05333927091820707</v>
+        <v>-0.1560210459680674</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06193296883128202</v>
+        <v>-0.07576971907306876</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.002542176931835613</v>
+        <v>0.03494587690185881</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02117029940761414</v>
+        <v>-0.1390909402977464</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
@@ -7052,64 +7052,64 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01676347329249835</v>
+        <v>0.004192482635898288</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.007962736831700883</v>
+        <v>0.1816897963104693</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.0431096353281832</v>
+        <v>-0.05042636206493903</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01848613207375739</v>
+        <v>0.08559598515413516</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.02915498660768847</v>
+        <v>0.04936751620329156</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03868340008267526</v>
+        <v>-0.06965238738974078</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01074578402245424</v>
+        <v>-0.02559779339047125</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.04801609140726026</v>
+        <v>0.03329206803295635</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7118,28 +7118,28 @@
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03492730158898554</v>
+        <v>-0.04652155560476381</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01800853324538329</v>
+        <v>-0.1207863360948215</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.01273240932661513</v>
+        <v>0.01381219093374771</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,61 +7151,61 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04031058507127145</v>
+        <v>-0.182084278895533</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.00219608616129765</v>
+        <v>0.009131390685529537</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.05051323756887752</v>
+        <v>0.1372612639522513</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02337114818320961</v>
+        <v>0.1305428991179473</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.007294898108296374</v>
+        <v>-0.06885930959363282</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.03220326931927844</v>
+        <v>0.1418539790983374</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.004338661111028134</v>
+        <v>0.08825685363775429</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,37 +7214,37 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.03431021427251858</v>
+        <v>-0.1004635350829509</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0273020740168135</v>
+        <v>-0.04078768382954054</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002412328263166297</v>
+        <v>-0.03316002188059819</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.01857309936957559</v>
+        <v>0.1841810902217411</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1348259697433015</v>
+        <v>0.3373987394478324</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04379506189043564</v>
+        <v>-0.007585653330811648</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08594514106985895</v>
+        <v>-0.1720814810777267</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1106125208022328</v>
+        <v>0.4011324919732094</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02919938703112965</v>
+        <v>-0.1072592638374752</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.05405982675771129</v>
+        <v>-0.1409340287233288</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01637509852854037</v>
+        <v>0.1185312693205919</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.009989386400224492</v>
+        <v>-0.1548268864143918</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01484456207940539</v>
+        <v>-0.03557929142555117</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.00248783655619208</v>
+        <v>-0.04076176209024474</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.001527775506781476</v>
+        <v>-0.2464650610797348</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.008563603731603458</v>
+        <v>0.06177018022025802</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01636597738937083</v>
+        <v>0.03517981373258483</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0137103254712804</v>
+        <v>-0.05096223616330912</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01455420392242464</v>
+        <v>0.001760389904881438</v>
       </c>
       <c r="AQ13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1237483496821287</v>
+        <v>0.47563181543282</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03488746721861532</v>
+        <v>-0.279771399974085</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.05794618582723716</v>
+        <v>-0.171337311526472</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04883396289626291</v>
+        <v>-0.04991524523678179</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,40 +7432,40 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.05506809484599268</v>
+        <v>0.00684039542961495</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06543933737898666</v>
+        <v>-0.09400788091526967</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.04497201160190367</v>
+        <v>0.06284374711418773</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02414179771973033</v>
+        <v>0.09289244567112977</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02040155489670076</v>
+        <v>0.002858999962701885</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.06139182194665552</v>
+        <v>0.2643094839227052</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01016641649851479</v>
+        <v>-0.07991694747759778</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.01405901117375665</v>
+        <v>-0.1118372476465697</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,58 +7498,58 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.02858424881559696</v>
+        <v>-0.1316199361834546</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003123879519418482</v>
+        <v>0.02267051137208377</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02627497304633851</v>
+        <v>0.06923940697131185</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.004499995299475237</v>
+        <v>-0.06944374337110762</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.007289415388179154</v>
+        <v>0.08159784507120466</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.003452961181780618</v>
+        <v>0.07194861379260885</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
@@ -7558,46 +7558,46 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.01905755845409543</v>
+        <v>-0.1331114031175034</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005238747820629988</v>
+        <v>0.01235663676617125</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02719832761075089</v>
+        <v>0.09244986109440102</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.0333962509912266</v>
+        <v>-0.04859270879292264</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0311868144942959</v>
+        <v>-0.1850538533278084</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.001896583360313668</v>
+        <v>0.03195062878612484</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
@@ -7609,22 +7609,22 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.005514900411274951</v>
+        <v>-0.02433791948197067</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.002357894440868449</v>
+        <v>-0.102067564773239</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01096043213651559</v>
+        <v>0.07266421118236224</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.03297960486399233</v>
+        <v>-0.02212547449692655</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01862117572703724</v>
+        <v>-0.002862296023255115</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01212265196906851</v>
+        <v>0.01548700988879589</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7663,64 +7663,64 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02835599544120531</v>
+        <v>-0.05985041982219882</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01113948141402222</v>
+        <v>0.01830547761379703</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02832260495877352</v>
+        <v>0.003450993648967088</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01203830737553718</v>
+        <v>-0.02280619424219154</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02463332573720139</v>
+        <v>0.001867932015099797</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.005673897951104398</v>
+        <v>0.1507591971864721</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.02002811900716256</v>
+        <v>-0.1474980863936873</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,13 +7729,13 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0092226521776322</v>
+        <v>-0.002407750523633103</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03234831855472367</v>
+        <v>0.05838663227245517</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,25 +7747,25 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02134701730175617</v>
+        <v>0.2115159355124017</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01758589504084824</v>
+        <v>-0.05132033559195938</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01414636415694452</v>
+        <v>0.158076123934048</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,52 +7774,52 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00508011221544545</v>
+        <v>0.07384518933521585</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02431119838537231</v>
+        <v>-0.09879249339748111</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.0002925942208924221</v>
+        <v>-0.05705688746756553</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.00287530653128033</v>
+        <v>-0.04092778477740124</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01461270366511266</v>
+        <v>0.09199005364616408</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,22 +7830,22 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3302977240661358</v>
+        <v>0.4807809591386235</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.06833603011801445</v>
+        <v>-0.2443509842196717</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1024854754163753</v>
+        <v>-0.1135356818562062</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
@@ -7854,25 +7854,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2174530785935297</v>
+        <v>0.4676599319511661</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.05301430827059399</v>
+        <v>-0.2137041082299993</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.09410111553790425</v>
+        <v>-0.2040032264495515</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1041788498868478</v>
+        <v>0.1047121150327694</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.005008010402479494</v>
+        <v>-0.05665813875879073</v>
       </c>
       <c r="W14" t="n">
-        <v>0.05051843179346067</v>
+        <v>-0.142216665758688</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -7911,43 +7911,43 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.08297799023495532</v>
+        <v>-0.04339992676566112</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01077680731380392</v>
+        <v>-0.1685086467375592</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.04876286836202214</v>
+        <v>-0.1573734265822685</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01652293002753765</v>
+        <v>0.1660444196204692</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.07472583066068937</v>
+        <v>-0.1566540706482327</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06413987785762044</v>
+        <v>0.02149737718375116</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7956,25 +7956,25 @@
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3405859721761988</v>
+        <v>0.4671438366786226</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.001554162597947286</v>
+        <v>-0.2786961007206488</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.09258071048776799</v>
+        <v>-0.454751517967428</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7983,34 +7983,34 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0007103151917949103</v>
+        <v>-0.05153131961066028</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.03943895508626637</v>
+        <v>-0.04406215935938082</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.182824577445299</v>
+        <v>0.07330169317362292</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,76 +8019,76 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.05658346984644287</v>
+        <v>0.03800530764878571</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05950187721017283</v>
+        <v>0.1437113485040025</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1686412725658097</v>
+        <v>0.02573981894951212</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1740532866460317</v>
+        <v>0.3476248132726025</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0319277663140269</v>
+        <v>-0.2181036416868151</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.03797985959729799</v>
+        <v>-0.1510738455296278</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.08451779687926983</v>
+        <v>-0.1727380562958032</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.007275276509596404</v>
+        <v>0.2182748741601159</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0101686426355948</v>
+        <v>0.03216504162972194</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,49 +8100,49 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.007858606096766734</v>
+        <v>-0.07414749062794822</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.04344048690726267</v>
+        <v>0.1766003271866099</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.03501391140731662</v>
+        <v>0.06082456125797463</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.07093544750140153</v>
+        <v>-0.1628980996402416</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02970246141458681</v>
+        <v>0.2281649156811577</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01301883140526802</v>
+        <v>0.05051017661747478</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.0125196152699711</v>
+        <v>-0.1516252973085384</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.003677134908222871</v>
+        <v>-0.02013899702647747</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.04036757523595359</v>
+        <v>-0.1786343029675522</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8178,46 +8178,46 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.01230690430546273</v>
+        <v>-0.1191567620203951</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.1103602576057209</v>
+        <v>0.04467509669162336</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.04711465275903131</v>
+        <v>-0.0008674921857578514</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.03551622466810223</v>
+        <v>0.02638507216903691</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02226182742370168</v>
+        <v>0.1125273932536583</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03721120706116117</v>
+        <v>-0.04897655114038253</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8226,85 +8226,85 @@
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.09216041978681719</v>
+        <v>-0.09630649308582143</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.04131683454523528</v>
+        <v>0.1601100387503865</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.09902451848149407</v>
+        <v>0.05317399166303943</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.06186603682240514</v>
+        <v>-0.0973816010815884</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.06286597411485582</v>
+        <v>-0.1538635804145743</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01917853968389636</v>
+        <v>-0.01357842765330335</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.06944541059931759</v>
+        <v>-0.1917592144905057</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.009438294202456315</v>
+        <v>0.2600448390889469</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.02272489277595312</v>
+        <v>0.0183605526600189</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8313,19 +8313,19 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01383569442245218</v>
+        <v>0.1807454920941711</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.05936710636785527</v>
+        <v>0.1990913557816331</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01369586781006172</v>
+        <v>-0.01768089611296377</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,31 +8334,31 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.007269486000870287</v>
+        <v>0.04962374795557711</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.07170670334889009</v>
+        <v>0.2907018257632596</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.003004898711628783</v>
+        <v>-0.08883921729868453</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
@@ -8367,39 +8367,39 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0209022467115928</v>
+        <v>-0.07295262892023523</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06823526480643301</v>
+        <v>0.1561149623122186</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2676993126039623</v>
+        <v>0.4017715231632873</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06671496833637849</v>
+        <v>0.0246932119011675</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1918608293621701</v>
+        <v>-0.3831278484016971</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2166068974659366</v>
+        <v>0.4710647226599242</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.01494713008897566</v>
+        <v>-0.1436084044174686</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1234629670989375</v>
+        <v>-0.3371346101398127</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03181408728572357</v>
+        <v>0.1320299599051998</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
@@ -8462,37 +8462,37 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03971595399192946</v>
+        <v>-0.08527809754568716</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.001347999107294765</v>
+        <v>-0.09239702214784011</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.00662782574207151</v>
+        <v>-0.08580383050724147</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.007093869098271577</v>
+        <v>-0.257656986944564</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.02110677343113558</v>
+        <v>0.07467748145648018</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03383078706902921</v>
+        <v>0.1383294412198395</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.009233705475709017</v>
+        <v>-0.04958611367038201</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.06326500597547371</v>
+        <v>-0.09146859857006927</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,37 +8531,37 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1905668425321045</v>
+        <v>0.6297704803701913</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.04739832321297288</v>
+        <v>-0.3150410813343302</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.1449362667424685</v>
+        <v>-0.3360639718717255</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.06690721928282724</v>
+        <v>-0.1325805625032121</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,10 +8570,10 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.05841539499133237</v>
+        <v>0.004483679845595459</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.07528272945317747</v>
+        <v>-0.0517598253592754</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
@@ -8582,13 +8582,13 @@
         <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.06125856409976967</v>
+        <v>0.1298945646412827</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
@@ -8597,118 +8597,118 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.03075465273804261</v>
+        <v>0.06117125787318747</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01195487285070227</v>
+        <v>0.07403361031557863</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1085079209900496</v>
+        <v>0.3519622828322963</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.03167366989002865</v>
+        <v>-0.09506169406629322</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.044611852675548</v>
+        <v>-0.1952125120893284</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.05306706838307551</v>
+        <v>-0.1608307765919066</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.0008251679259424682</v>
+        <v>0.05289861126716448</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.04974248194331121</v>
+        <v>0.1101217136219521</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.00101926267783676</v>
+        <v>-0.1417368972218091</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.0007615528269792495</v>
+        <v>0.1793868661272933</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.02769652351567361</v>
+        <v>-0.01499409612693199</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.04687730112414662</v>
+        <v>-0.1541152813551738</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.002807330394818862</v>
+        <v>0.03121858338983003</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.05291806062609888</v>
+        <v>0.1438280368084429</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8717,40 +8717,40 @@
         <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.007552772947573142</v>
+        <v>0.02402716904458923</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07238762126906718</v>
+        <v>-0.03592436555550672</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.004998404619916944</v>
+        <v>0.03941054773144995</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02648176832302917</v>
+        <v>-0.1344615590541565</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,37 +8759,37 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02233243320046989</v>
+        <v>0.03222823511298151</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.009762137182064539</v>
+        <v>0.181888781248509</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05400175770283632</v>
+        <v>-0.09988151531978631</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02627418857717933</v>
+        <v>0.1246134066710156</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.03544010511685861</v>
+        <v>0.05231829979432972</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8798,25 +8798,25 @@
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.04875393263593245</v>
+        <v>-0.0245384249916443</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01452451516034062</v>
+        <v>-0.05066425665112808</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.04958603429870949</v>
+        <v>0.003909690480142736</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
@@ -8825,13 +8825,13 @@
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.04055236037653223</v>
+        <v>-0.02643944039167207</v>
       </c>
       <c r="EQ15" t="n">
         <v>-0</v>
@@ -8840,13 +8840,13 @@
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.009825714988686925</v>
+        <v>-0.1247433463772089</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.001855118663794039</v>
+        <v>0.02862507763874947</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,61 +8858,61 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.04743759783810186</v>
+        <v>-0.1800875070450378</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.006685243391145719</v>
+        <v>0.02482490249984299</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.05081046677096548</v>
+        <v>0.1302488128525351</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.02797409550623245</v>
+        <v>0.1254017864052943</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01040955346967613</v>
+        <v>-0.04508059131903399</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.03757818373629235</v>
+        <v>0.1622720744584939</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.001511565851981456</v>
+        <v>0.03000139795053225</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,37 +8921,37 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03319133338476846</v>
+        <v>-0.09186736493196045</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.02779671635757965</v>
+        <v>-0.02496357206239757</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.003893560544839046</v>
+        <v>-0.03834146479403726</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.01948278165072459</v>
+        <v>0.1608377277565259</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,46 +8968,46 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3914387973627113</v>
+        <v>0.3080781210347568</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1292321226168123</v>
+        <v>-0.03670274990891691</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09138808101574299</v>
+        <v>-0.04867600648145461</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06849954048338529</v>
+        <v>-0.089255373673195</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3096314531084942</v>
+        <v>0.3723935974587326</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07914379471230611</v>
+        <v>-0.09354487959353117</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05711312086504966</v>
+        <v>-0.1613155342893801</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06082013665470763</v>
+        <v>-0.07130007069821498</v>
       </c>
       <c r="P16" t="n">
         <v>-0</v>
@@ -9016,160 +9016,160 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0797585920436306</v>
+        <v>0.08485242987316534</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.03159139576174904</v>
+        <v>-0.08338128876081909</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04321032422246961</v>
+        <v>-0.09334176698863779</v>
       </c>
       <c r="X16" t="n">
-        <v>0.008281868801082903</v>
+        <v>-0.04082881348477928</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.05469476147964637</v>
+        <v>-0.08341130080924621</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.00603605476953405</v>
+        <v>-0.1043798524330551</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0106803824483597</v>
+        <v>-0.127131401071791</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.02304969649044112</v>
+        <v>0.006630997532220738</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02005733751311313</v>
+        <v>0.08338148995310406</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.05822256633474839</v>
+        <v>-0.06089830124664408</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.05946877122054375</v>
+        <v>-0.01415736908197287</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.04972403419047933</v>
+        <v>0.003449000074499492</v>
       </c>
       <c r="AQ16" t="n">
         <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3147686602751004</v>
+        <v>0.31429086266913</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.04163851791113492</v>
+        <v>-0.05908753718531376</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.02864131875391492</v>
+        <v>-0.1846235439727412</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01207150899931441</v>
+        <v>-0.08932270540460026</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.06832443092625019</v>
+        <v>-0.01438578427077991</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.07217007516465397</v>
+        <v>-0.07791529726211641</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1182485866358672</v>
+        <v>-0.0401868474688744</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.06950617590522067</v>
+        <v>-0.1169922057321055</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.08719621984085445</v>
+        <v>0.02773380800757204</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05043649942166353</v>
+        <v>0.09400752012195236</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1122955324299812</v>
+        <v>0.01379362405518521</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.04152287562358898</v>
+        <v>-0.02670571758537815</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
@@ -9178,55 +9178,55 @@
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1473307808932945</v>
+        <v>0.212105287439123</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0.002053554015757335</v>
+        <v>-0.06256928086141615</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.02747331522995456</v>
+        <v>-0.05571795874965433</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.01155974808243367</v>
+        <v>-0.09786923846840721</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.08074540858791235</v>
+        <v>-0.08784789600818223</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.01074165617061295</v>
+        <v>0.03582176883418085</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0001120366566356612</v>
+        <v>0.01105407974499711</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.03088078869073627</v>
+        <v>0.04597604085999782</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,52 +9235,52 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.009185642810980693</v>
+        <v>-0.04800781587784975</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.04323835258731098</v>
+        <v>0.124727690703105</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.04782421539104371</v>
+        <v>0.07415791433918695</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.03692848509786104</v>
+        <v>0.07686408175782955</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.06416014554779696</v>
+        <v>-0.09353193411806426</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.03491810918599714</v>
+        <v>0.05706720089551582</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.004623674327814494</v>
+        <v>0.006760208280848052</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03160603881021872</v>
+        <v>0.06574257266983756</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
@@ -9292,19 +9292,19 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03495666566363965</v>
+        <v>-0.03884094054741728</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.05221915977518067</v>
+        <v>-0.006023548968673684</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.005634595112333718</v>
+        <v>0.01420869450606629</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.009437300559003683</v>
+        <v>0.01727039187776782</v>
       </c>
       <c r="DK16" t="n">
         <v>-0</v>
@@ -9316,79 +9316,79 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.02050257087969024</v>
+        <v>-0.02163396383720913</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.04227869389841259</v>
+        <v>0.03946503998625037</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.01816412858087591</v>
+        <v>-0.04691527953659277</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.01789450968354055</v>
+        <v>0.06283711884469523</v>
       </c>
       <c r="DT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.04381584787434219</v>
+        <v>0.004044672247187018</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.018823023157281</v>
+        <v>0.066020790920328</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.02971074382450228</v>
+        <v>-0.06671148054262251</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.03945891986157966</v>
+        <v>0.03362927935053524</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.08206353258813559</v>
+        <v>-0.02168555345463847</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.03385239042302574</v>
+        <v>0.02217287439168169</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.05787396998950029</v>
+        <v>0.004361806312144651</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.02777678497280656</v>
+        <v>-0.02500307216824414</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,52 +9397,52 @@
         <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.06043544099664602</v>
+        <v>-0.04538102158083815</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.02139009594246384</v>
+        <v>0.01809510018386322</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02496163012165199</v>
+        <v>-0.004551970882301812</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0343777376163501</v>
+        <v>0.1235592656498461</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.06490605388883304</v>
+        <v>-0.09434004682959085</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.01456524678515596</v>
+        <v>0.06680094220786581</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.009721286292105414</v>
+        <v>-0.00894478901084407</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03899879420015542</v>
+        <v>0.04160967125827059</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
@@ -9451,49 +9451,49 @@
         <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.03384124664619439</v>
+        <v>0.1388247551220854</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.04752122015785781</v>
+        <v>0.1037075660486925</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01644328167173518</v>
+        <v>-0.06692663417532112</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.008628744689709989</v>
+        <v>0.1264326313646575</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.004207213453942889</v>
+        <v>0.01313906499955786</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.006457410582206165</v>
+        <v>0.09929545915050833</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.03869808715367874</v>
+        <v>-0.03815243587750026</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01789119393053079</v>
+        <v>-0.004111226963875264</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
@@ -9502,34 +9502,34 @@
         <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.02168097623248078</v>
+        <v>0.01726571440869279</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.06038965803849938</v>
+        <v>-0.07608759758481268</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.04219389356240705</v>
+        <v>0.08505539208371313</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,46 +9537,46 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2777824512919211</v>
+        <v>0.1770089386957001</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09233271161490433</v>
+        <v>-0.1180472101028701</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01701954546092467</v>
+        <v>-0.006117140190156687</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1935557667776318</v>
+        <v>0.2063902165009304</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09150547049459362</v>
+        <v>-0.1302009811676089</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03433872346452936</v>
+        <v>-0.03753664696247427</v>
       </c>
       <c r="O17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9591,16 +9591,16 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07245526674479894</v>
+        <v>0.04906526252067289</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01507085003545158</v>
+        <v>-0.03452796343181355</v>
       </c>
       <c r="W17" t="n">
-        <v>0.07302734627384153</v>
+        <v>-0.04003204543785014</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -9612,22 +9612,22 @@
         <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.06105638304526673</v>
+        <v>-0.03484864609926368</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.02682478090430404</v>
+        <v>-0.08478192235507719</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.01571139093683693</v>
+        <v>-0.05641373710268534</v>
       </c>
       <c r="AG17" t="n">
         <v>-0</v>
@@ -9636,109 +9636,109 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.01336230233808672</v>
+        <v>0.06546703551777955</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.05858973808684054</v>
+        <v>-0.06969981959011588</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.0497640747042304</v>
+        <v>0.02652506755916883</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2424611429252096</v>
+        <v>0.1863685141950621</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.02413180077717192</v>
+        <v>-0.05946662056486866</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.09799989036637115</v>
+        <v>-0.1165402352581731</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.02407958170378169</v>
+        <v>-0.006237318863585724</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.1095740048766374</v>
+        <v>-0.03726958828381096</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.06646378102914004</v>
+        <v>-0.01061861863806503</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.06617317623080068</v>
+        <v>0.006036321838700802</v>
       </c>
       <c r="BN17" t="n">
         <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.02920860800778403</v>
+        <v>0.03153727893819264</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.1485172905580161</v>
+        <v>0.03727030385658302</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>0</v>
@@ -9747,49 +9747,49 @@
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.110761780118191</v>
+        <v>0.1339803747602816</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.03177099465494644</v>
+        <v>-0.06246429100252355</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.06825638884265145</v>
+        <v>-0.01383423679131079</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.05629157379400163</v>
+        <v>-0.05168705966483712</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.00107908944583109</v>
+        <v>0.06855427977408661</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.00882333574409268</v>
+        <v>0.00275803186089691</v>
       </c>
       <c r="CI17" t="n">
         <v>0</v>
@@ -9801,76 +9801,76 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.01426989820413448</v>
+        <v>-0.04778881377768956</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.04784427152661226</v>
+        <v>0.1200820869142796</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.06990498035187109</v>
+        <v>0.02732418205488828</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
         <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.04154676356222466</v>
+        <v>-0.04781011108191123</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.01564418922031125</v>
+        <v>0.07482703921996567</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.009714719832509246</v>
+        <v>0.008042308933358309</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.03413422010400868</v>
+        <v>-0.03787287981512873</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.01680345209203656</v>
+        <v>0.03923610635326566</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01718003109977203</v>
+        <v>-0.03598195738353999</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9888,16 +9888,16 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.02469420081283781</v>
+        <v>-0.03720325962351487</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.06027095608988734</v>
+        <v>-0.03459042572468192</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.02173523962570828</v>
+        <v>-0.001378049285865848</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -9906,85 +9906,85 @@
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.05119619421356296</v>
+        <v>-0.005839631306262947</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.0002785806439680183</v>
+        <v>0.05134804901852995</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.03280398903929443</v>
+        <v>-0.04576373124788359</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0570615646529291</v>
+        <v>-0.02267648862347208</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.02272933817161915</v>
+        <v>0.04473112586116616</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.05338438727946628</v>
+        <v>0.03395170852707208</v>
       </c>
       <c r="EK17" t="n">
         <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.04145842870648406</v>
+        <v>-0.001450907583512939</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01699837934633264</v>
+        <v>0.03042084778568056</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.02413430857724541</v>
+        <v>-0.03563913020898556</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,22 +9993,22 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.04328574665326884</v>
+        <v>-0.05436070975952335</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0.002810857415313174</v>
+        <v>0.08628454165312015</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.00621336876100595</v>
+        <v>-0.008860156421911699</v>
       </c>
       <c r="FC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -10017,22 +10017,22 @@
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.04487115567059423</v>
+        <v>0.06841969174556667</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.01216995746829308</v>
+        <v>0.05468366950198535</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0546361856249953</v>
+        <v>-0.02851862767170693</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10041,28 +10041,28 @@
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.0017861927316125</v>
+        <v>0.0007065843840244324</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.008944445822141919</v>
+        <v>0.07620999590579938</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.004536506483118027</v>
+        <v>-0.01467077210878024</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
         <v>0</v>
@@ -10074,39 +10074,39 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.02099008425814784</v>
+        <v>-0.01971075221396421</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.08860955999583681</v>
+        <v>0.02844827822207514</v>
       </c>
       <c r="GC17" t="n">
         <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2843260731085602</v>
+        <v>0.4267367756940705</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07629568575223157</v>
+        <v>0.03346450691596674</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1505925481805898</v>
+        <v>-0.3188769356913924</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -10127,13 +10127,13 @@
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.236926680909485</v>
+        <v>0.5368647266733635</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,25 +10142,25 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03422178605415858</v>
+        <v>-0.07049502785296537</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1340490413544676</v>
+        <v>-0.3831377184901614</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.03172499151153871</v>
+        <v>0.1407399671883814</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,40 +10169,40 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.02742753303234861</v>
+        <v>-0.07800404404421868</v>
       </c>
       <c r="X18" t="n">
-        <v>0.006659234844407969</v>
+        <v>-0.07496468563482311</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002645644667846701</v>
+        <v>-0.04988684382279795</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01908694765908388</v>
+        <v>-0.2859590668106995</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.001661731448322688</v>
+        <v>0.08538994902834801</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10211,25 +10211,25 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.03203098239681457</v>
+        <v>0.109910871395536</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.008440134803329639</v>
+        <v>-0.07178318899116827</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.05345173775006735</v>
+        <v>-0.07622901944104633</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,37 +10238,37 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1760845481031086</v>
+        <v>0.5948092735104112</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.02584782470675553</v>
+        <v>-0.3412715884312488</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.08355267257204106</v>
+        <v>-0.2445843538585451</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.05481192508733461</v>
+        <v>-0.08840453522317254</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,64 +10277,64 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.06157189795381435</v>
+        <v>0.01652514162899651</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.05563620332872208</v>
+        <v>-0.0596002214098944</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.04114262019233813</v>
+        <v>0.1002049726626364</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.01349591946773963</v>
+        <v>0.04884593648423356</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01917535245866475</v>
+        <v>0.04374862200906651</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.09175166752960284</v>
+        <v>0.3380635490289614</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.02796830781708763</v>
+        <v>-0.05549725043335735</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.02408979630116703</v>
+        <v>-0.1467671173277338</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,28 +10343,28 @@
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD18" t="n">
         <v>0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.05117751644561428</v>
+        <v>-0.1357209651226546</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.00372832594609396</v>
+        <v>0.03041921838953823</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.03308748227264278</v>
+        <v>0.1018134632560909</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,49 +10376,49 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.004822747584826596</v>
+        <v>-0.1808962729497087</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.01602459082465275</v>
+        <v>0.2105709037735922</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.04440504760308618</v>
+        <v>0.03929107508992982</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.04586486574060541</v>
+        <v>-0.1290112819215544</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.004280800781493841</v>
+        <v>0.01725827958388886</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.03623571390976237</v>
+        <v>0.1331505519204463</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
@@ -10430,19 +10430,19 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.04121676697346308</v>
+        <v>-0.1033367256041787</v>
       </c>
       <c r="DG18" t="n">
         <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.04718688368898347</v>
+        <v>-0.07678710480414734</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.01961940221368216</v>
+        <v>0.05612762820646137</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,13 +10451,13 @@
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.0225449084646726</v>
+        <v>-0.07135208804688692</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
@@ -10466,16 +10466,16 @@
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01820886167380321</v>
+        <v>-0.008134555916778573</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.003620435473011496</v>
+        <v>0.111885489785036</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,76 +10484,76 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.04347065913829567</v>
+        <v>-0.03128082408227935</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01408318050171589</v>
+        <v>-0.007911325724990351</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.02945185419372622</v>
+        <v>0.02881908206303176</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.05016620317182836</v>
+        <v>-0.04963122538015106</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.01740178647284765</v>
+        <v>-0.01431627955363004</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.02752450876448287</v>
+        <v>0.01696877335550949</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.03534261536428319</v>
+        <v>-0.05870587912215686</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.02476181158128654</v>
+        <v>-0.07363231487462793</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.0004441270170850627</v>
+        <v>-0.003209863432623836</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10565,52 +10565,52 @@
         <v>0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.04655729515271426</v>
+        <v>-0.1540862631670359</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.002694894946018624</v>
+        <v>-0.007015633041871021</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03587917621551068</v>
+        <v>0.1138590349732119</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01622897465863704</v>
+        <v>0.1231205726715829</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.01138588566897179</v>
+        <v>-0.07103289929011392</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.03127015842491836</v>
+        <v>0.1714206279201776</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.0008029277346391496</v>
+        <v>0.01298193325874547</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,37 +10628,37 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.002154112431568427</v>
+        <v>-0.008796779166785177</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.03308174334464212</v>
+        <v>-0.07607478910259322</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.002277158297694669</v>
+        <v>-0.02714364945379507</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.03143499827454987</v>
+        <v>0.1583746588854772</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1523536413646175</v>
+        <v>0.2907847890048133</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,25 +10684,25 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05709564210544144</v>
+        <v>0.001671006422345624</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07469972131117288</v>
+        <v>-0.1009675943093347</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1283986212823652</v>
+        <v>0.3506309414280351</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,10 +10711,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.04781124884454727</v>
+        <v>-0.06781315609812544</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.06843707478869797</v>
+        <v>-0.1244825199135092</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -10723,55 +10723,55 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01226551168347378</v>
+        <v>0.06404051346131771</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.009125059065088119</v>
+        <v>-0.0524508496693999</v>
       </c>
       <c r="X19" t="n">
-        <v>0.009519170002364812</v>
+        <v>-0.006370575291186326</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.008433938176578672</v>
+        <v>-0.03321770747455526</v>
       </c>
       <c r="AD19" t="n">
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.02055775960759068</v>
+        <v>-0.1670682444301154</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.005790285215451289</v>
+        <v>0.01160278157393618</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI19" t="n">
         <v>-0</v>
@@ -10783,22 +10783,22 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.01042697923094485</v>
+        <v>0.02448310127652997</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.009241985191073214</v>
+        <v>-0.02091661010259217</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.01306569413608864</v>
+        <v>0.001840477573829747</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10807,10 +10807,10 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.09673796084558586</v>
+        <v>0.2525081126048492</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
@@ -10819,25 +10819,25 @@
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.01286490282650813</v>
+        <v>-0.1845436262548232</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.02658348750225081</v>
+        <v>-0.08891156147865707</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.03454014605148271</v>
+        <v>0.01433318190419384</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,52 +10846,52 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.04867295587891129</v>
+        <v>-0.0005037104729998637</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.05704502018165574</v>
+        <v>-0.03991626520497332</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.03278544106584474</v>
+        <v>0.01272514067054394</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.01650580381249848</v>
+        <v>0.0415915268751021</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.02010148662685906</v>
+        <v>-0.02179493314373466</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.04618194622705196</v>
+        <v>0.1443007449026777</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -10900,10 +10900,10 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.01036607105200665</v>
+        <v>-0.03298962294616768</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.007259735715660311</v>
+        <v>-0.07243167079719361</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10915,28 +10915,28 @@
         <v>-0</v>
       </c>
       <c r="CD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.02255988511389562</v>
+        <v>-0.07075413886925704</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.003991973832606628</v>
+        <v>0.0151437774045167</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.01885477706877093</v>
+        <v>0.03731140005277928</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.004845224399292627</v>
+        <v>-0.06958282608580557</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
@@ -10954,67 +10954,67 @@
         <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.00166449890213543</v>
+        <v>0.1128087954689455</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.01039527785806808</v>
+        <v>0.05188082400729004</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.0177298376066304</v>
+        <v>-0.07046123845873141</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.004677105243729456</v>
+        <v>0.007242227890377088</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.01853781809322859</v>
+        <v>0.05237196739220941</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.03218569985663485</v>
+        <v>-0.04776813554299245</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.0195485981623542</v>
+        <v>-0.1069992378431678</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.009823486982341163</v>
+        <v>0.03725814618921845</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL19" t="n">
         <v>-0</v>
@@ -11026,34 +11026,34 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.007348691585913716</v>
+        <v>-0.01142032333022853</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.02020388762672191</v>
+        <v>-0.03466259390624436</v>
       </c>
       <c r="DS19" t="n">
-        <v>-0.006426071792263331</v>
+        <v>0.02824442318586308</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.02883051079312595</v>
+        <v>0.008673600135567007</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
@@ -11062,40 +11062,40 @@
         <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.01516404375926808</v>
+        <v>-0.06193888100224826</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.008369553167946317</v>
+        <v>0.01584615924816907</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
       </c>
       <c r="ED19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.02708923669788185</v>
+        <v>-0.03949649278674288</v>
       </c>
       <c r="EH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.005847175795744002</v>
+        <v>0.01414028605676306</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.01584689717400456</v>
+        <v>-0.001849259761638515</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
         <v>-0</v>
@@ -11104,22 +11104,22 @@
         <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.00894396810526155</v>
+        <v>-0.02599981276406655</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>8.914991101654245e-05</v>
+        <v>-0.007318410837752925</v>
       </c>
       <c r="ET19" t="n">
-        <v>0.001416905808285733</v>
+        <v>0.07196762173913444</v>
       </c>
       <c r="EU19" t="n">
         <v>0</v>
@@ -11128,58 +11128,58 @@
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.01799459294550992</v>
+        <v>-0.08254369337441593</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.007821289159169707</v>
+        <v>-0.002473718365152283</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.02297560418215991</v>
+        <v>0.03131256720802424</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>-0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.01629930458609554</v>
+        <v>0.1189647632900024</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.01106060995979267</v>
+        <v>-0.0660491957128292</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.01682425162300366</v>
+        <v>0.08232934213031724</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
@@ -11188,55 +11188,55 @@
         <v>0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>0.0004464365600760502</v>
+        <v>0.005506376371652235</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.003437237440851204</v>
+        <v>-0.01501968347910372</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.007271843193774078</v>
+        <v>-0.02626097522000694</v>
       </c>
       <c r="FV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.001855684338953209</v>
+        <v>-0.02795730028088251</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
         <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.009407922832489181</v>
+        <v>0.04718044985359195</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
         <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
